--- a/Result/profitability/2506.xlsx
+++ b/Result/profitability/2506.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,13 +669,13 @@
         <v>0.11</v>
       </c>
       <c r="M2" t="n">
-        <v>0.31625</v>
+        <v>0.02125</v>
       </c>
       <c r="N2" t="n">
-        <v>43.57874999999999</v>
+        <v>42.19125</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0.04</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001250000000000002</v>
+        <v>0.0625</v>
       </c>
       <c r="N3" t="n">
-        <v>38.96124999999999</v>
+        <v>39.94749999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.18</v>
       </c>
       <c r="M4" t="n">
-        <v>0.015</v>
+        <v>0.01375000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>37.20499999999999</v>
+        <v>34.55499999999999</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.05</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0175</v>
+        <v>0.03625</v>
       </c>
       <c r="N5" t="n">
-        <v>32.30249999999999</v>
+        <v>31.85124999999999</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.17</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0325</v>
+        <v>0.04875</v>
       </c>
       <c r="N6" t="n">
-        <v>29.37874999999999</v>
+        <v>31.19124999999999</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1149,7 +1149,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.2</v>
       </c>
       <c r="M7" t="n">
-        <v>0.04875</v>
+        <v>0.07750000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>29.26124999999999</v>
+        <v>28.80124999999999</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>0.06125000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>26.55624999999999</v>
+        <v>25.36999999999999</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.05</v>
       </c>
       <c r="M9" t="n">
-        <v>0.05125000000000001</v>
+        <v>0.05125</v>
       </c>
       <c r="N9" t="n">
         <v>22.76124999999999</v>
@@ -1645,7 +1645,7 @@
         <v>0.01</v>
       </c>
       <c r="M10" t="n">
-        <v>0.03875000000000001</v>
+        <v>0.03875</v>
       </c>
       <c r="N10" t="n">
         <v>22.54624999999999</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2506</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>483</v>
+      </c>
+      <c r="D75" t="n">
+        <v>278</v>
+      </c>
+      <c r="E75" t="n">
+        <v>206</v>
+      </c>
+      <c r="F75" t="n">
+        <v>42.56</v>
+      </c>
+      <c r="G75" t="n">
+        <v>83</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>17.22%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>14</v>
+      </c>
+      <c r="J75" t="n">
+        <v>97</v>
+      </c>
+      <c r="K75" t="n">
+        <v>72</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.3275</v>
+      </c>
+      <c r="N75" t="n">
+        <v>45.89624999999999</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-9.489999999999995</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1823246878001921</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.869565217391304</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-3.609999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.07818930041152261</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
